--- a/Backlog-HE-EPPAT-Peruri.xlsx
+++ b/Backlog-HE-EPPAT-Peruri.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="2167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="2171">
   <si>
     <t>Panduan Penerapan IDDS untuk Developer E-PPAT</t>
   </si>
@@ -6735,6 +6735,18 @@
   </si>
   <si>
     <t>prototipe/Backlog-HE-MINUTA-V2-Prototype.html; sumber/sidebar-seragam.js; semua prototipe tenant dan HE</t>
+  </si>
+  <si>
+    <t>Warna ikon menu samping disesuaikan dengan aturan warna IDDS (teks dan ikon memakai color family yang sama): ikon kini mengikuti warna teks menunya, yaitu putih redup saat biasa dan putih saat disorot atau aktif, menggantikan ikon emas #C2BB4B. Warna brand E-PPAT tetap tampil pada latar menu samping, menu aktif, dan kartu profil kantor. Uji kontras lulus.</t>
+  </si>
+  <si>
+    <t>sumber/order-idds.html; sumber/tera-idds.html; semua prototipe tenant dan HE</t>
+  </si>
+  <si>
+    <t>Semua ikon di luar menu samping (tombol, tabel, dialog, lencana, isian, kartu kantor, remah, dan index) diganti dengan Tabler Icons resmi versi 3.19.0, pustaka ikon IDDS. Sebanyak 112 jenis ikon dipetakan ke ikon Tabler yang paling dekat maknanya; audit isi SVG menunjukkan 0 ikon non-Tabler. Logo, ilustrasi, peta, kode QR, dan grafik tidak diubah.</t>
+  </si>
+  <si>
+    <t>sumber/aset/tabler-ui.json; sumber/ikon-tabler.js; semua prototipe</t>
   </si>
   <si>
     <t>Keterangan</t>
@@ -23212,7 +23224,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -24187,6 +24199,34 @@
       </c>
       <c r="D71" s="6" t="s">
         <v>2119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="35">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="35">
+        <v>46322</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>2123</v>
       </c>
     </row>
   </sheetData>
@@ -24210,19 +24250,19 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2121</v>
+        <v>2125</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>27</v>
@@ -24230,10 +24270,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>2123</v>
+        <v>2127</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>2124</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -24241,55 +24281,55 @@
         <v>1881</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>2129</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>2130</v>
+        <v>2134</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>2131</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>2137</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -24302,7 +24342,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>2138</v>
+        <v>2142</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>27</v>
@@ -24310,26 +24350,26 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>2140</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>2141</v>
+        <v>2145</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>2143</v>
+        <v>2147</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>2144</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -24337,7 +24377,7 @@
         <v>517</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>2145</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -24345,7 +24385,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -24369,7 +24409,7 @@
         <v>1886</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -24377,7 +24417,7 @@
         <v>541</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -24385,7 +24425,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -24393,7 +24433,7 @@
         <v>1887</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -24401,7 +24441,7 @@
         <v>1888</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -24409,7 +24449,7 @@
         <v>1889</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -24417,7 +24457,7 @@
         <v>1890</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -24430,7 +24470,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
       <c r="B30" s="36" t="s">
         <v>27</v>
@@ -24438,7 +24478,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="37" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
       <c r="B31" s="37" t="s">
         <v>1933</v>
@@ -24446,7 +24486,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
       <c r="B32" s="37" t="s">
         <v>1935</v>
@@ -24454,7 +24494,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
       <c r="B33" s="37" t="s">
         <v>1937</v>
@@ -24462,7 +24502,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
       <c r="B34" s="37" t="s">
         <v>1939</v>
@@ -24470,15 +24510,15 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
-        <v>2159</v>
+        <v>2163</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>2160</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>2161</v>
+        <v>2165</v>
       </c>
       <c r="B36" s="37" t="s">
         <v>1943</v>
@@ -24486,7 +24526,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="B37" s="37" t="s">
         <v>1945</v>
@@ -24494,7 +24534,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="B38" s="37" t="s">
         <v>1947</v>
@@ -24502,7 +24542,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="B39" s="37" t="s">
         <v>1949</v>
@@ -24510,7 +24550,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>2165</v>
+        <v>2169</v>
       </c>
       <c r="B40" s="37" t="s">
         <v>1951</v>
@@ -24518,7 +24558,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
-        <v>2166</v>
+        <v>2170</v>
       </c>
       <c r="B41" s="37" t="s">
         <v>1953</v>

--- a/Backlog-HE-EPPAT-Peruri.xlsx
+++ b/Backlog-HE-EPPAT-Peruri.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="2171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3625" uniqueCount="2188">
   <si>
     <t>Panduan Penerapan IDDS untuk Developer E-PPAT</t>
   </si>
@@ -4418,6 +4418,27 @@
     <t>Hanya menu yang ada di live. Tugas Saya, Permohonan APHT, Arsip Akta, dan Template Akta belum ada di live sehingga belum ditambahkan.</t>
   </si>
   <si>
+    <t>IDDS-TN-41</t>
+  </si>
+  <si>
+    <t>Tema Tampilan: tiga preset tema IDDS (E-PPAT, INAgov, Default)</t>
+  </si>
+  <si>
+    <t>Sembilan preset warna bebas dalam satu daftar tanpa pembeda brand IDDS: Navy Dark, e-PPAT Teal (bawaan), Navy Blue ("Biru dongker standar IDDS"), Sky Blue, Deep Blue, Royal Blue, Crimson, Steel Blue, dan Burgundy. Label "Navy Blue: standar IDDS" tidak akurat karena standar IDDS adalah Default netral dan INAgov biru #0956C3. Merah (Crimson, Burgundy) dapat dipilih sebagai warna utama tanpa peringatan, padahal berisiko salah makna.</t>
+  </si>
+  <si>
+    <t>Preset Brand dibagi dua kelompok IDDS Radio. Kelompok teratas "Preset tema IDDS" berlencana "Sesuai IDDS" dan direkomendasikan. Isinya "E-PPAT (bawaan)" (hijau #3D6B5E, menggantikan "e-PPAT Teal"), "INAgov" (biru #0956C3, brand bawaan IDDS), dan "Default IDDS" (abu-abu netral bawaan IDDS). Ketiganya dikonfirmasi Peruri sebagai penyedia IDDS. Setiap kartu punya contoh warna dan keterangan kapan dipakai. Memilih preset langsung mengubah Pratinjau Langsung: wadah pratinjau memakai data-brand yang sama dengan aplikasi (eppat, inagov, atau tanpa data-brand untuk Default). Preset live lainnya tetap ada di kelompok "Warna lain (di luar brand IDDS)" dengan keterangan "Warna ini bukan brand resmi IDDS. Pastikan kontrasnya lulus sebelum dipakai." Crimson dan Burgundy diberi peringatan kecil karena IDDS memakai merah untuk galat dan aksi hapus. Label Navy Blue menjadi "Biru dongker". Mode Kustom, penanda belum disimpan, konfirmasi Batal, dan Toast simpan tetap.</t>
+  </si>
+  <si>
+    <t>dev-app.eppat.id/t/&lt;kantor&gt; › Konten Situs › Tema Tampilan › Preset</t>
+  </si>
+  <si>
+    <t>Tema Tampilan menyediakan tiga preset tema IDDS (E-PPAT, INAgov, Default IDDS). Memilih preset langsung mengubah pratinjau, dan semua teks pada ketiga tema lulus uji kontras WCAG AA.</t>
+  </si>
+  <si>
+    <t>Ketiga pilihan tema dikonfirmasi Peruri sebagai penyedia IDDS (27 Okt 2026).</t>
+  </si>
+  <si>
     <t>Penyesuaian IDDS · Platform (admin platform)</t>
   </si>
   <si>
@@ -5081,6 +5102,27 @@
     <t>Struktur sama dengan menu samping tenant (IDDS-TN-40) dan Onboarding (IDDS-OB-11).</t>
   </si>
   <si>
+    <t>IDDS-PL-42</t>
+  </si>
+  <si>
+    <t>Platform · Setting Theme (penyesuaian IDDS)</t>
+  </si>
+  <si>
+    <t>Setting Theme: tiga preset tema IDDS (E-PPAT, INAgov, Default)</t>
+  </si>
+  <si>
+    <t>Preset Brand dibagi dua kelompok IDDS Radio. Kelompok teratas "Preset tema IDDS" berlencana "Sesuai IDDS" dan direkomendasikan. Isinya "E-PPAT (bawaan)" (hijau #3D6B5E, menggantikan "e-PPAT Teal"), "INAgov" (biru #0956C3, brand bawaan IDDS), dan "Default IDDS" (abu-abu netral bawaan IDDS). Ketiganya dikonfirmasi Peruri sebagai penyedia IDDS. Setiap kartu punya contoh warna dan keterangan kapan dipakai. Memilih preset langsung mengubah Pratinjau Langsung: wadah pratinjau memakai data-brand yang sama dengan aplikasi (eppat, inagov, atau tanpa data-brand untuk Default). Preset live lainnya tetap ada di kelompok "Warna lain (di luar brand IDDS)" dengan keterangan "Warna ini bukan brand resmi IDDS. Pastikan kontrasnya lulus sebelum dipakai." Crimson dan Burgundy diberi peringatan kecil karena IDDS memakai merah untuk galat dan aksi hapus. Label Navy Blue menjadi "Biru dongker". Mode Kustom, penanda belum disimpan, konfirmasi Batal, dan Toast simpan tetap. Pola sama persis dengan Tema Tampilan kantor (IDDS-TN-41).</t>
+  </si>
+  <si>
+    <t>dev-app.eppat.id/platform › Setting Theme › Preset</t>
+  </si>
+  <si>
+    <t>Setting Theme platform menyediakan tiga preset tema IDDS yang sama dengan tenant (E-PPAT, INAgov, Default IDDS), dengan pratinjau langsung dan kontras yang lulus WCAG AA.</t>
+  </si>
+  <si>
+    <t>Pola sama dengan IDDS-TN-41.</t>
+  </si>
+  <si>
     <t>Penyesuaian IDDS · Onboarding (calon PPAT dan staf Onboarding)</t>
   </si>
   <si>
@@ -6747,6 +6789,15 @@
   </si>
   <si>
     <t>sumber/aset/tabler-ui.json; sumber/ikon-tabler.js; semua prototipe</t>
+  </si>
+  <si>
+    <t>IDDS-TN-41; IDDS-PL-42</t>
+  </si>
+  <si>
+    <t>Tiga pilihan tema yang dikonfirmasi Peruri sebagai penyedia IDDS (E-PPAT, INAgov, Default IDDS) disediakan di dua tempat: (1) pilihan Tema di bilah semua prototipe untuk diskusi internal, tersimpan dan terbawa antarprototipe; (2) preset di Tema Tampilan tenant dan Setting Theme Platform, dikelompokkan menjadi Preset tema IDDS (berlencana Sesuai IDDS) dan Warna lain di luar brand IDDS. Label Navy Blue standar IDDS dikoreksi, Crimson dan Burgundy diberi peringatan karena merah dipakai untuk galat. Uji kontras ketiga tema lulus.</t>
+  </si>
+  <si>
+    <t>sumber/tema-proto.html; sumber/rakit-idds.js; prototipe/Backlog-IDDS-TN-CMS-Prototype.html; Backlog-IDDS-PL-SISTEM-Prototype.html; semua prototipe</t>
   </si>
   <si>
     <t>Keterangan</t>
@@ -16063,2112 +16114,43 @@
         <v>46321</v>
       </c>
     </row>
-    <row r="45" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="203" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="204" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="205" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="206" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="207" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="208" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="209" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="210" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="211" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="213" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="214" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="215" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="216" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="217" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="218" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="219" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="220" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="221" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="222" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="223" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="224" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="225" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="226" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="227" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="228" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="229" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="230" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="231" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="232" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="233" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="234" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="235" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="237" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="238" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="239" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="240" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="241" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="242" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="243" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="245" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="249" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="252" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="253" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="255" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="256" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="257" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="258" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="259" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="266" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="267" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="270" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="273" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="274" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="275" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="276" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="277" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="278" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="279" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="280" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="281" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="282" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="283" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="284" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="285" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="286" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="287" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="288" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="289" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="291" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="292" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="293" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="294" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="295" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="296" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="297" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="298" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="299" spans="7:11" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="7:11" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <autoFilter ref="A4:M44"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:F3"/>
-  </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="G10:G300">
-      <formula1>"Tinggi,Sedang,Rendah"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G5:G300">
-      <formula1>"Tinggi,Sedang,Rendah"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K10:K300">
-      <formula1>"Usulan,Prototipe siap,Perlu konfirmasi,Disetujui,Dikerjakan developer,Selesai,Ditunda"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K5:K300">
-      <formula1>"Usulan,Prototipe siap,Perlu konfirmasi,Disetujui,Dikerjakan developer,Selesai,Ditunda"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M300"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="45" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="32" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1348</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/index.html#platform","Situs prototipe: https://he-eppat.vercel.app/  ·  Buka daftar prototipe kelompok ini")</f>
-        <v>Situs prototipe: https://he-eppat.vercel.app/  ·  Buka daftar prototipe kelompok ini</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>1</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>1351</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>1352</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>1353</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I5" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>1355</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M5" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>2</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>1358</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>1359</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I6" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>1361</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M6" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>1363</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>1364</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>1365</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I7" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>1366</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M7" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
-        <v>4</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>1367</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>1368</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>1369</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I8" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>1371</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M8" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>1373</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>1374</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I9" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>1376</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M9" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
-        <v>6</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>1379</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>1380</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I10" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>1381</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M10" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>1383</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>1384</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>1385</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I11" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>1386</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M11" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
-        <v>8</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>1388</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>1389</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>1390</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I12" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>1391</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M12" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>9</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>1393</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>1394</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>1395</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I13" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>1396</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M13" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
-        <v>10</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>1397</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>1398</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>1399</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>1400</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I14" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>1401</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M14" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>11</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>1404</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>1405</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I15" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>1408</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M15" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
-        <v>12</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>1410</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>1411</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>1412</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>1413</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I16" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>1414</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M16" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>13</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>1415</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>1416</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I17" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>1419</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M17" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
-        <v>14</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>1421</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>1422</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I18" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>1424</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M18" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>15</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>1426</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I19" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>1429</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M19" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
-        <v>16</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>1430</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>1431</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>1433</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I20" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>1434</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M20" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>17</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>1435</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>1436</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>1437</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>1438</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I21" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>1439</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M21" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
-        <v>18</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>1441</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>1443</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I22" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>1444</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M22" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
-        <v>19</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>1445</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>1446</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>1447</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>1448</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I23" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>1449</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M23" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
-        <v>20</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>1451</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>1452</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>1453</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>1407</v>
-      </c>
-      <c r="I24" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>1454</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>1409</v>
-      </c>
-      <c r="M24" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
-        <v>21</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>1455</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>1458</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>1459</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I25" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>1461</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
-        <v>22</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>1463</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>1465</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I26" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>1466</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M26" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
-        <v>23</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>1467</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>1468</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>1470</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I27" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>1471</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="14">
-        <v>24</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>1473</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>1475</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I28" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>1476</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
-        <v>25</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>1477</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>1478</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>1480</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I29" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>1481</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M29" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
-        <v>26</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>1483</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I30" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>1486</v>
-      </c>
-      <c r="K30" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
-        <v>27</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>1487</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>1488</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>1490</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I31" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>1491</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
-        <v>28</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>1493</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>1495</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I32" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>1496</v>
-      </c>
-      <c r="K32" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M32" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
-        <v>29</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>1497</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>1498</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>1500</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I33" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K33" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M33" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
-        <v>30</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>1503</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>1505</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>1460</v>
-      </c>
-      <c r="I34" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>1506</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L34" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M34" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
-        <v>31</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>1509</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I35" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>1513</v>
-      </c>
-      <c r="K35" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>1514</v>
-      </c>
-      <c r="M35" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
-        <v>32</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>1516</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I36" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>1519</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>1514</v>
-      </c>
-      <c r="M36" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="10">
-        <v>33</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>1520</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>1521</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>1523</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I37" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>1524</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>1514</v>
-      </c>
-      <c r="M37" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
-        <v>34</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>1525</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>1526</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>1528</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I38" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>1529</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M38" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
-        <v>35</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>1531</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>1533</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I39" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>1534</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L39" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M39" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="14">
-        <v>36</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>1535</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>1536</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>1537</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>1538</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I40" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>1539</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M40" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
-        <v>37</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>1541</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>1543</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I41" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>1544</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L41" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M41" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="14">
-        <v>38</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>1546</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>1547</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>1548</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I42" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>1549</v>
-      </c>
-      <c r="K42" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M42" s="16">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
-        <v>39</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>1551</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>1552</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>1553</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I43" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>1554</v>
-      </c>
-      <c r="K43" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L43" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M43" s="13">
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="14">
-        <v>40</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>1556</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>1558</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>1512</v>
-      </c>
-      <c r="I44" s="14" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>1559</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M44" s="16">
-        <v>46321</v>
-      </c>
-    </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>41</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1560</v>
+        <v>1347</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1561</v>
+        <v>1205</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1562</v>
+        <v>1348</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>1563</v>
+        <v>1349</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>1564</v>
+        <v>1350</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>1565</v>
+        <v>1351</v>
       </c>
       <c r="I45" s="10" t="str">
-        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
-        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-TN-CMS-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-TN-CMS-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-TN-CMS-Prototype.html</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>1566</v>
+        <v>1352</v>
       </c>
       <c r="K45" s="12" t="s">
         <v>541</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>1567</v>
+        <v>1353</v>
       </c>
       <c r="M45" s="13">
         <v>46321</v>
@@ -18456,6 +16438,2157 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M300"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="6" width="55" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="45" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="32" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/index.html#platform","Situs prototipe: https://he-eppat.vercel.app/  ·  Buka daftar prototipe kelompok ini")</f>
+        <v>Situs prototipe: https://he-eppat.vercel.app/  ·  Buka daftar prototipe kelompok ini</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I5" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>1362</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M5" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I6" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>1368</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M6" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I7" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>1373</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M7" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <v>4</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I8" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M8" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I9" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M9" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I10" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>1388</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M10" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I11" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M11" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>8</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I12" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>1398</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M12" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I13" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M13" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>10</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>1361</v>
+      </c>
+      <c r="I14" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MASUK-Prototype.html</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>1408</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M14" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I15" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M15" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <v>12</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I16" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M16" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>13</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I17" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M17" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>14</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I18" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M18" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>15</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I19" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>1436</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M19" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <v>16</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M20" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>17</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I21" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M21" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <v>18</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I22" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>1451</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M22" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <v>19</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I23" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>1456</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M23" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <v>20</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I24" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>1461</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M24" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I25" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>1468</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <v>22</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I26" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>1473</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>23</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I27" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <v>24</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I28" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>1483</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M28" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>25</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I29" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M29" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <v>26</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I30" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>27</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I31" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>1498</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M31" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <v>28</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>1502</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I32" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>1503</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M32" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
+        <v>29</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I33" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>1508</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <v>30</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>1467</v>
+      </c>
+      <c r="I34" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-AKTA-Prototype.html</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>1513</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="10">
+        <v>31</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I35" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>1520</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="M35" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>32</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I36" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>1526</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="M36" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="10">
+        <v>33</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>1530</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I37" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="M37" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <v>34</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I38" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>1536</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
+        <v>35</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I39" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>1541</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M39" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <v>36</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I40" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>1546</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
+        <v>37</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I41" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M41" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <v>38</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I42" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
+        <v>39</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I43" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <v>40</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I44" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M44" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
+        <v>41</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I45" s="10" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-MONITORING-Prototype.html</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>1574</v>
+      </c>
+      <c r="M45" s="13">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <v>42</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>1579</v>
+      </c>
+      <c r="I46" s="14" t="str">
+        <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html")</f>
+        <v>https://he-eppat.vercel.app/Backlog-IDDS-PL-SISTEM-Prototype.html</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L46" s="12" t="s">
+        <v>1581</v>
+      </c>
+      <c r="M46" s="16">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="47" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="7:11" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="7:11" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <autoFilter ref="A4:M46"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="G10:G300">
+      <formula1>"Tinggi,Sedang,Rendah"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G5:G300">
+      <formula1>"Tinggi,Sedang,Rendah"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:K300">
+      <formula1>"Usulan,Prototipe siap,Perlu konfirmasi,Disetujui,Dikerjakan developer,Selesai,Ditunda"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K5:K300">
+      <formula1>"Usulan,Prototipe siap,Perlu konfirmasi,Disetujui,Dikerjakan developer,Selesai,Ditunda"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M300"/>
@@ -18478,7 +18611,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1568</v>
+        <v>1582</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18495,7 +18628,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -18567,32 +18700,32 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1572</v>
+        <v>1586</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1574</v>
+        <v>1588</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I5" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1576</v>
+        <v>1590</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>541</v>
@@ -18609,32 +18742,32 @@
         <v>2</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1577</v>
+        <v>1591</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>1580</v>
+        <v>1594</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I6" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>541</v>
@@ -18651,32 +18784,32 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1582</v>
+        <v>1596</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1583</v>
+        <v>1597</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I7" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>1586</v>
+        <v>1600</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>541</v>
@@ -18693,32 +18826,32 @@
         <v>4</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>1587</v>
+        <v>1601</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1588</v>
+        <v>1602</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1589</v>
+        <v>1603</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>1590</v>
+        <v>1604</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I8" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>541</v>
@@ -18735,32 +18868,32 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1592</v>
+        <v>1606</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1593</v>
+        <v>1607</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>1594</v>
+        <v>1608</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I9" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>1596</v>
+        <v>1610</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>541</v>
@@ -18777,32 +18910,32 @@
         <v>6</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>1597</v>
+        <v>1611</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1598</v>
+        <v>1612</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1599</v>
+        <v>1613</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I10" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>1601</v>
+        <v>1615</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>541</v>
@@ -18819,32 +18952,32 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1603</v>
+        <v>1617</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>1604</v>
+        <v>1618</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>1605</v>
+        <v>1619</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I11" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>541</v>
@@ -18861,32 +18994,32 @@
         <v>8</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>1607</v>
+        <v>1621</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1608</v>
+        <v>1622</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>1610</v>
+        <v>1624</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I12" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>541</v>
@@ -18903,32 +19036,32 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1612</v>
+        <v>1626</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1613</v>
+        <v>1627</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I13" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>1616</v>
+        <v>1630</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>541</v>
@@ -18945,32 +19078,32 @@
         <v>10</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>1617</v>
+        <v>1631</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1618</v>
+        <v>1632</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>1619</v>
+        <v>1633</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="I14" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MASUK-Prototype.html</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>1621</v>
+        <v>1635</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>541</v>
@@ -18987,32 +19120,32 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1624</v>
+        <v>1638</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>1626</v>
+        <v>1640</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I15" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>1628</v>
+        <v>1642</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>541</v>
@@ -19029,32 +19162,32 @@
         <v>12</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>1629</v>
+        <v>1643</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>1630</v>
+        <v>1644</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1631</v>
+        <v>1645</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>1632</v>
+        <v>1646</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I16" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>1633</v>
+        <v>1647</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>541</v>
@@ -19071,32 +19204,32 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1634</v>
+        <v>1648</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1635</v>
+        <v>1649</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1636</v>
+        <v>1650</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>1637</v>
+        <v>1651</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I17" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>1638</v>
+        <v>1652</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>541</v>
@@ -19113,32 +19246,32 @@
         <v>14</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>1639</v>
+        <v>1653</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>1640</v>
+        <v>1654</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>1641</v>
+        <v>1655</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>1642</v>
+        <v>1656</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I18" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>1643</v>
+        <v>1657</v>
       </c>
       <c r="K18" s="12" t="s">
         <v>541</v>
@@ -19155,32 +19288,32 @@
         <v>15</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1644</v>
+        <v>1658</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1645</v>
+        <v>1659</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1646</v>
+        <v>1660</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1647</v>
+        <v>1661</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I19" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>1648</v>
+        <v>1662</v>
       </c>
       <c r="K19" s="12" t="s">
         <v>541</v>
@@ -19197,32 +19330,32 @@
         <v>16</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>1649</v>
+        <v>1663</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>1650</v>
+        <v>1664</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>1651</v>
+        <v>1665</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>1652</v>
+        <v>1666</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I20" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>1653</v>
+        <v>1667</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>541</v>
@@ -19239,32 +19372,32 @@
         <v>17</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1654</v>
+        <v>1668</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1655</v>
+        <v>1669</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1656</v>
+        <v>1670</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1657</v>
+        <v>1671</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I21" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>1658</v>
+        <v>1672</v>
       </c>
       <c r="K21" s="12" t="s">
         <v>541</v>
@@ -19281,32 +19414,32 @@
         <v>18</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>1659</v>
+        <v>1673</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>1660</v>
+        <v>1674</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>1661</v>
+        <v>1675</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>1662</v>
+        <v>1676</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I22" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>1663</v>
+        <v>1677</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>541</v>
@@ -19323,32 +19456,32 @@
         <v>19</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1664</v>
+        <v>1678</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1665</v>
+        <v>1679</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>1666</v>
+        <v>1680</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>1667</v>
+        <v>1681</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I23" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>1668</v>
+        <v>1682</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>541</v>
@@ -19365,32 +19498,32 @@
         <v>20</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>1669</v>
+        <v>1683</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>1670</v>
+        <v>1684</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>1671</v>
+        <v>1685</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>1672</v>
+        <v>1686</v>
       </c>
       <c r="G24" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="I24" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-MONITOR-Prototype.html</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>1673</v>
+        <v>1687</v>
       </c>
       <c r="K24" s="12" t="s">
         <v>541</v>
@@ -19407,32 +19540,32 @@
         <v>21</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1674</v>
+        <v>1688</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1676</v>
+        <v>1690</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>1677</v>
+        <v>1691</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>1678</v>
+        <v>1692</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I25" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>1680</v>
+        <v>1694</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>541</v>
@@ -19449,32 +19582,32 @@
         <v>22</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>1681</v>
+        <v>1695</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>1682</v>
+        <v>1696</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>1683</v>
+        <v>1697</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>1684</v>
+        <v>1698</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I26" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>1685</v>
+        <v>1699</v>
       </c>
       <c r="K26" s="12" t="s">
         <v>541</v>
@@ -19491,32 +19624,32 @@
         <v>23</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>1686</v>
+        <v>1700</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1687</v>
+        <v>1701</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>1688</v>
+        <v>1702</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>1689</v>
+        <v>1703</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I27" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>1690</v>
+        <v>1704</v>
       </c>
       <c r="K27" s="12" t="s">
         <v>541</v>
@@ -19533,32 +19666,32 @@
         <v>24</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>1691</v>
+        <v>1705</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>1692</v>
+        <v>1706</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>1693</v>
+        <v>1707</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>1694</v>
+        <v>1708</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I28" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>1695</v>
+        <v>1709</v>
       </c>
       <c r="K28" s="12" t="s">
         <v>541</v>
@@ -19575,32 +19708,32 @@
         <v>25</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>1696</v>
+        <v>1710</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1697</v>
+        <v>1711</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>1698</v>
+        <v>1712</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>1699</v>
+        <v>1713</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I29" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>1700</v>
+        <v>1714</v>
       </c>
       <c r="K29" s="12" t="s">
         <v>541</v>
@@ -19617,32 +19750,32 @@
         <v>26</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>1701</v>
+        <v>1715</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>1702</v>
+        <v>1716</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>1703</v>
+        <v>1717</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>1704</v>
+        <v>1718</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I30" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>1705</v>
+        <v>1719</v>
       </c>
       <c r="K30" s="12" t="s">
         <v>541</v>
@@ -19659,32 +19792,32 @@
         <v>27</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>1706</v>
+        <v>1720</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1707</v>
+        <v>1721</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>1708</v>
+        <v>1722</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>1709</v>
+        <v>1723</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I31" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>1710</v>
+        <v>1724</v>
       </c>
       <c r="K31" s="12" t="s">
         <v>541</v>
@@ -19701,32 +19834,32 @@
         <v>28</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>1711</v>
+        <v>1725</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>1712</v>
+        <v>1726</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>1713</v>
+        <v>1727</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>1714</v>
+        <v>1728</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I32" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>1715</v>
+        <v>1729</v>
       </c>
       <c r="K32" s="12" t="s">
         <v>541</v>
@@ -19743,32 +19876,32 @@
         <v>29</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1716</v>
+        <v>1730</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1717</v>
+        <v>1731</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>1718</v>
+        <v>1732</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>1719</v>
+        <v>1733</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I33" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>1720</v>
+        <v>1734</v>
       </c>
       <c r="K33" s="12" t="s">
         <v>541</v>
@@ -19785,32 +19918,32 @@
         <v>30</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>1721</v>
+        <v>1735</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>1722</v>
+        <v>1736</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>1671</v>
+        <v>1685</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>1723</v>
+        <v>1737</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="I34" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-VERIF-Prototype.html</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>1724</v>
+        <v>1738</v>
       </c>
       <c r="K34" s="12" t="s">
         <v>541</v>
@@ -19827,32 +19960,32 @@
         <v>31</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1725</v>
+        <v>1739</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1727</v>
+        <v>1741</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>1728</v>
+        <v>1742</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>1729</v>
+        <v>1743</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I35" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>1731</v>
+        <v>1745</v>
       </c>
       <c r="K35" s="12" t="s">
         <v>541</v>
@@ -19869,32 +20002,32 @@
         <v>32</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>1732</v>
+        <v>1746</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>1733</v>
+        <v>1747</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>1734</v>
+        <v>1748</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>1735</v>
+        <v>1749</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I36" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>1736</v>
+        <v>1750</v>
       </c>
       <c r="K36" s="12" t="s">
         <v>541</v>
@@ -19911,32 +20044,32 @@
         <v>33</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1737</v>
+        <v>1751</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>1738</v>
+        <v>1752</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>1739</v>
+        <v>1753</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>1740</v>
+        <v>1754</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I37" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>1741</v>
+        <v>1755</v>
       </c>
       <c r="K37" s="12" t="s">
         <v>541</v>
@@ -19953,32 +20086,32 @@
         <v>34</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>1743</v>
+        <v>1757</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>1744</v>
+        <v>1758</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>1745</v>
+        <v>1759</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I38" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>1746</v>
+        <v>1760</v>
       </c>
       <c r="K38" s="12" t="s">
         <v>541</v>
@@ -19995,32 +20128,32 @@
         <v>35</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1747</v>
+        <v>1761</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1748</v>
+        <v>1762</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>1749</v>
+        <v>1763</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>1750</v>
+        <v>1764</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I39" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>1751</v>
+        <v>1765</v>
       </c>
       <c r="K39" s="12" t="s">
         <v>541</v>
@@ -20037,32 +20170,32 @@
         <v>36</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>1752</v>
+        <v>1766</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>1753</v>
+        <v>1767</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>1754</v>
+        <v>1768</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>1755</v>
+        <v>1769</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I40" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>1756</v>
+        <v>1770</v>
       </c>
       <c r="K40" s="12" t="s">
         <v>541</v>
@@ -20079,32 +20212,32 @@
         <v>37</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>1757</v>
+        <v>1771</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>1758</v>
+        <v>1772</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>1759</v>
+        <v>1773</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>1760</v>
+        <v>1774</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I41" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>1761</v>
+        <v>1775</v>
       </c>
       <c r="K41" s="12" t="s">
         <v>541</v>
@@ -20121,32 +20254,32 @@
         <v>38</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>1762</v>
+        <v>1776</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>1763</v>
+        <v>1777</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>1764</v>
+        <v>1778</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>1765</v>
+        <v>1779</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I42" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>1766</v>
+        <v>1780</v>
       </c>
       <c r="K42" s="12" t="s">
         <v>541</v>
@@ -20163,32 +20296,32 @@
         <v>39</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1767</v>
+        <v>1781</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>1768</v>
+        <v>1782</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>1769</v>
+        <v>1783</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>1770</v>
+        <v>1784</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I43" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>1771</v>
+        <v>1785</v>
       </c>
       <c r="K43" s="12" t="s">
         <v>541</v>
@@ -20205,32 +20338,32 @@
         <v>40</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>1772</v>
+        <v>1786</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>1773</v>
+        <v>1787</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>1774</v>
+        <v>1788</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>1775</v>
+        <v>1789</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I44" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>1776</v>
+        <v>1790</v>
       </c>
       <c r="K44" s="12" t="s">
         <v>541</v>
@@ -20247,32 +20380,32 @@
         <v>41</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>1777</v>
+        <v>1791</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1778</v>
+        <v>1792</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>1779</v>
+        <v>1793</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>1780</v>
+        <v>1794</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I45" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>1781</v>
+        <v>1795</v>
       </c>
       <c r="K45" s="12" t="s">
         <v>541</v>
@@ -20289,32 +20422,32 @@
         <v>42</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>1782</v>
+        <v>1796</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>1783</v>
+        <v>1797</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>1784</v>
+        <v>1798</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>1785</v>
+        <v>1799</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I46" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>1786</v>
+        <v>1800</v>
       </c>
       <c r="K46" s="12" t="s">
         <v>541</v>
@@ -20331,32 +20464,32 @@
         <v>43</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>1787</v>
+        <v>1801</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>1788</v>
+        <v>1802</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>1789</v>
+        <v>1803</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>1790</v>
+        <v>1804</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I47" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>1791</v>
+        <v>1805</v>
       </c>
       <c r="K47" s="12" t="s">
         <v>541</v>
@@ -20373,32 +20506,32 @@
         <v>44</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>1792</v>
+        <v>1806</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>1793</v>
+        <v>1807</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>1794</v>
+        <v>1808</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>1795</v>
+        <v>1809</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I48" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>1796</v>
+        <v>1810</v>
       </c>
       <c r="K48" s="12" t="s">
         <v>541</v>
@@ -20415,32 +20548,32 @@
         <v>45</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>1797</v>
+        <v>1811</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>1798</v>
+        <v>1812</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>1799</v>
+        <v>1813</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>1800</v>
+        <v>1814</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="I49" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-PENGATURAN-Prototype.html</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>1801</v>
+        <v>1815</v>
       </c>
       <c r="K49" s="12" t="s">
         <v>541</v>
@@ -20457,32 +20590,32 @@
         <v>46</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>1802</v>
+        <v>1816</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>1804</v>
+        <v>1818</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>1805</v>
+        <v>1819</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>1806</v>
+        <v>1820</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I50" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>1808</v>
+        <v>1822</v>
       </c>
       <c r="K50" s="12" t="s">
         <v>541</v>
@@ -20499,32 +20632,32 @@
         <v>47</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>1809</v>
+        <v>1823</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1810</v>
+        <v>1824</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>1811</v>
+        <v>1825</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>1812</v>
+        <v>1826</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I51" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>1813</v>
+        <v>1827</v>
       </c>
       <c r="K51" s="12" t="s">
         <v>541</v>
@@ -20541,32 +20674,32 @@
         <v>48</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>1814</v>
+        <v>1828</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>1815</v>
+        <v>1829</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>1816</v>
+        <v>1830</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>1817</v>
+        <v>1831</v>
       </c>
       <c r="G52" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I52" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>1818</v>
+        <v>1832</v>
       </c>
       <c r="K52" s="12" t="s">
         <v>541</v>
@@ -20583,32 +20716,32 @@
         <v>49</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>1819</v>
+        <v>1833</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1820</v>
+        <v>1834</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>1821</v>
+        <v>1835</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>1822</v>
+        <v>1836</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I53" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>1823</v>
+        <v>1837</v>
       </c>
       <c r="K53" s="12" t="s">
         <v>541</v>
@@ -20625,32 +20758,32 @@
         <v>50</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>1824</v>
+        <v>1838</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>1825</v>
+        <v>1839</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>1826</v>
+        <v>1840</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>1827</v>
+        <v>1841</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I54" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>1828</v>
+        <v>1842</v>
       </c>
       <c r="K54" s="12" t="s">
         <v>541</v>
@@ -20667,32 +20800,32 @@
         <v>51</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>1829</v>
+        <v>1843</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1830</v>
+        <v>1844</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>1831</v>
+        <v>1845</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>1832</v>
+        <v>1846</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I55" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>1833</v>
+        <v>1847</v>
       </c>
       <c r="K55" s="12" t="s">
         <v>541</v>
@@ -20709,32 +20842,32 @@
         <v>52</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>1834</v>
+        <v>1848</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>1835</v>
+        <v>1849</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>1836</v>
+        <v>1850</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>1837</v>
+        <v>1851</v>
       </c>
       <c r="G56" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I56" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>1838</v>
+        <v>1852</v>
       </c>
       <c r="K56" s="12" t="s">
         <v>541</v>
@@ -20751,32 +20884,32 @@
         <v>53</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>1839</v>
+        <v>1853</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1840</v>
+        <v>1854</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>1841</v>
+        <v>1855</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>1842</v>
+        <v>1856</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I57" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>1843</v>
+        <v>1857</v>
       </c>
       <c r="K57" s="12" t="s">
         <v>541</v>
@@ -20793,32 +20926,32 @@
         <v>54</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>1844</v>
+        <v>1858</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>1845</v>
+        <v>1859</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>1846</v>
+        <v>1860</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>1847</v>
+        <v>1861</v>
       </c>
       <c r="G58" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I58" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>1848</v>
+        <v>1862</v>
       </c>
       <c r="K58" s="12" t="s">
         <v>541</v>
@@ -20835,32 +20968,32 @@
         <v>55</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>1849</v>
+        <v>1863</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1850</v>
+        <v>1864</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>1851</v>
+        <v>1865</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>1852</v>
+        <v>1866</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I59" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>1853</v>
+        <v>1867</v>
       </c>
       <c r="K59" s="12" t="s">
         <v>541</v>
@@ -20877,32 +21010,32 @@
         <v>56</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>1854</v>
+        <v>1868</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>1855</v>
+        <v>1869</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>1856</v>
+        <v>1870</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>1857</v>
+        <v>1871</v>
       </c>
       <c r="G60" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I60" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>1858</v>
+        <v>1872</v>
       </c>
       <c r="K60" s="12" t="s">
         <v>541</v>
@@ -20919,32 +21052,32 @@
         <v>57</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>1859</v>
+        <v>1873</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>1860</v>
+        <v>1874</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>1861</v>
+        <v>1875</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>1862</v>
+        <v>1876</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I61" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>1863</v>
+        <v>1877</v>
       </c>
       <c r="K61" s="12" t="s">
         <v>541</v>
@@ -20961,32 +21094,32 @@
         <v>58</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>1864</v>
+        <v>1878</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>1865</v>
+        <v>1879</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>1866</v>
+        <v>1880</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>1867</v>
+        <v>1881</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I62" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>1868</v>
+        <v>1882</v>
       </c>
       <c r="K62" s="12" t="s">
         <v>541</v>
@@ -21003,32 +21136,32 @@
         <v>59</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>1869</v>
+        <v>1883</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>1870</v>
+        <v>1884</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>1871</v>
+        <v>1885</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>1872</v>
+        <v>1886</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>567</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I63" s="10" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>1873</v>
+        <v>1887</v>
       </c>
       <c r="K63" s="12" t="s">
         <v>541</v>
@@ -21045,32 +21178,32 @@
         <v>60</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>1874</v>
+        <v>1888</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>1803</v>
+        <v>1817</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>1875</v>
+        <v>1889</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>1876</v>
+        <v>1890</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>1877</v>
+        <v>1891</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>567</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>1807</v>
+        <v>1821</v>
       </c>
       <c r="I64" s="14" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html","https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html")</f>
         <v>https://he-eppat.vercel.app/Backlog-IDDS-OB-BAYAR-Prototype.html</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>1878</v>
+        <v>1892</v>
       </c>
       <c r="K64" s="12" t="s">
         <v>541</v>
@@ -21347,7 +21480,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -21356,7 +21489,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1879</v>
+        <v>1893</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -21366,7 +21499,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>1880</v>
+        <v>1894</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -21379,24 +21512,24 @@
         <v>528</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1884</v>
+        <v>1898</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1885</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>1886</v>
+        <v>1900</v>
       </c>
       <c r="B5" s="18">
         <f>COUNTIF('Usulan HE'!$N$5:$N$300,$A5)</f>
@@ -21429,11 +21562,11 @@
       </c>
       <c r="C6" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$K$5:$K$300,$A6)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$K$5:$K$300,$A6)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="18">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$K$5:$K$300,$A6)</f>
@@ -21441,7 +21574,7 @@
       </c>
       <c r="F6" s="18">
         <f>SUM(B6:E6)</f>
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -21471,7 +21604,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>1887</v>
+        <v>1901</v>
       </c>
       <c r="B8" s="18">
         <f>COUNTIF('Usulan HE'!$N$5:$N$300,$A8)</f>
@@ -21496,7 +21629,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>1888</v>
+        <v>1902</v>
       </c>
       <c r="B9" s="18">
         <f>COUNTIF('Usulan HE'!$N$5:$N$300,$A9)</f>
@@ -21521,7 +21654,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>1889</v>
+        <v>1903</v>
       </c>
       <c r="B10" s="18">
         <f>COUNTIF('Usulan HE'!$N$5:$N$300,$A10)</f>
@@ -21546,7 +21679,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>1890</v>
+        <v>1904</v>
       </c>
       <c r="B11" s="18">
         <f>COUNTIF('Usulan HE'!$N$5:$N$300,$A11)</f>
@@ -21571,7 +21704,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>1885</v>
+        <v>1899</v>
       </c>
       <c r="B12" s="19">
         <f>COUNTIF('Usulan HE'!$B$5:$B$300,"?*")</f>
@@ -21579,11 +21712,11 @@
       </c>
       <c r="C12" s="19">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$B$5:$B$300,"?*")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="19">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$B$5:$B$300,"?*")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="19">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$B$5:$B$300,"?*")</f>
@@ -21591,7 +21724,7 @@
       </c>
       <c r="F12" s="19">
         <f>SUM(B12:E12)</f>
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -21599,19 +21732,19 @@
         <v>525</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>1884</v>
+        <v>1898</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>1885</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -21649,11 +21782,11 @@
       </c>
       <c r="C16" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$G$5:$G$300,$A16)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$G$5:$G$300,$A16)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="18">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$G$5:$G$300,$A16)</f>
@@ -21661,7 +21794,7 @@
       </c>
       <c r="F16" s="18">
         <f>SUM(B16:E16)</f>
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -21691,13 +21824,13 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>1891</v>
+        <v>1905</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>1892</v>
+        <v>1906</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1893</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -21705,7 +21838,7 @@
         <v>532</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C20" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A20)</f>
@@ -21717,7 +21850,7 @@
         <v>436</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C21" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A21)</f>
@@ -21729,7 +21862,7 @@
         <v>411</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C22" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A22)</f>
@@ -21741,7 +21874,7 @@
         <v>665</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C23" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A23)</f>
@@ -21753,7 +21886,7 @@
         <v>722</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C24" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A24)</f>
@@ -21765,7 +21898,7 @@
         <v>768</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C25" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A25)</f>
@@ -21777,7 +21910,7 @@
         <v>416</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C26" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A26)</f>
@@ -21789,7 +21922,7 @@
         <v>837</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C27" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A27)</f>
@@ -21801,7 +21934,7 @@
         <v>891</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C28" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A28)</f>
@@ -21813,7 +21946,7 @@
         <v>927</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C29" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A29)</f>
@@ -21825,7 +21958,7 @@
         <v>954</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C30" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A30)</f>
@@ -21837,7 +21970,7 @@
         <v>981</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C31" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A31)</f>
@@ -21849,7 +21982,7 @@
         <v>1011</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="C32" s="18">
         <f>COUNTIF('Usulan HE'!$D$5:$D$300,A32)</f>
@@ -21861,7 +21994,7 @@
         <v>1097</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C33" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A33)</f>
@@ -21873,7 +22006,7 @@
         <v>1135</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C34" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A34)</f>
@@ -21885,7 +22018,7 @@
         <v>1147</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C35" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A35)</f>
@@ -21897,7 +22030,7 @@
         <v>1164</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C36" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A36)</f>
@@ -21909,7 +22042,7 @@
         <v>1171</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C37" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A37)</f>
@@ -21921,7 +22054,7 @@
         <v>1178</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C38" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A38)</f>
@@ -21933,7 +22066,7 @@
         <v>1190</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C39" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A39)</f>
@@ -21945,7 +22078,7 @@
         <v>1198</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C40" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A40)</f>
@@ -21957,11 +22090,11 @@
         <v>1205</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C41" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A41)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -21969,7 +22102,7 @@
         <v>1217</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C42" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A42)</f>
@@ -21981,7 +22114,7 @@
         <v>1224</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C43" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A43)</f>
@@ -21993,7 +22126,7 @@
         <v>1231</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C44" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A44)</f>
@@ -22005,7 +22138,7 @@
         <v>1239</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C45" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A45)</f>
@@ -22017,7 +22150,7 @@
         <v>1256</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C46" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A46)</f>
@@ -22029,7 +22162,7 @@
         <v>1267</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C47" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A47)</f>
@@ -22041,7 +22174,7 @@
         <v>1278</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C48" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A48)</f>
@@ -22053,7 +22186,7 @@
         <v>1285</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C49" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A49)</f>
@@ -22065,7 +22198,7 @@
         <v>1293</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C50" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A50)</f>
@@ -22077,7 +22210,7 @@
         <v>1300</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C51" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A51)</f>
@@ -22089,7 +22222,7 @@
         <v>1307</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C52" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A52)</f>
@@ -22101,7 +22234,7 @@
         <v>1315</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C53" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A53)</f>
@@ -22113,7 +22246,7 @@
         <v>1332</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C54" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A54)</f>
@@ -22125,7 +22258,7 @@
         <v>1340</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>1882</v>
+        <v>1896</v>
       </c>
       <c r="C55" s="18">
         <f>COUNTIF('Penyesuaian IDDS Tenant'!$C$5:$C$300,A55)</f>
@@ -22134,10 +22267,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="C56" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$C$5:$C$300,A56)</f>
@@ -22146,10 +22279,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>1403</v>
+        <v>1410</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="C57" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$C$5:$C$300,A57)</f>
@@ -22158,10 +22291,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="C58" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$C$5:$C$300,A58)</f>
@@ -22170,10 +22303,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="C59" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$C$5:$C$300,A59)</f>
@@ -22182,10 +22315,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>1883</v>
+        <v>1897</v>
       </c>
       <c r="C60" s="18">
         <f>COUNTIF('Penyesuaian IDDS Platform'!$C$5:$C$300,A60)</f>
@@ -22194,22 +22327,22 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>1884</v>
+        <v>1897</v>
       </c>
       <c r="C61" s="18">
-        <f>COUNTIF('Penyesuaian IDDS Onboarding'!$C$5:$C$300,A61)</f>
-        <v>10</v>
+        <f>COUNTIF('Penyesuaian IDDS Platform'!$C$5:$C$300,A61)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>1623</v>
+        <v>1585</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>1884</v>
+        <v>1898</v>
       </c>
       <c r="C62" s="18">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$C$5:$C$300,A62)</f>
@@ -22218,10 +22351,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>1675</v>
+        <v>1637</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>1884</v>
+        <v>1898</v>
       </c>
       <c r="C63" s="18">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$C$5:$C$300,A63)</f>
@@ -22230,25 +22363,37 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>1726</v>
+        <v>1689</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>1884</v>
+        <v>1898</v>
       </c>
       <c r="C64" s="18">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$C$5:$C$300,A64)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
-        <v>1803</v>
+        <v>1740</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>1884</v>
+        <v>1898</v>
       </c>
       <c r="C65" s="18">
         <f>COUNTIF('Penyesuaian IDDS Onboarding'!$C$5:$C$300,A65)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="18" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C66" s="18">
+        <f>COUNTIF('Penyesuaian IDDS Onboarding'!$C$5:$C$300,A66)</f>
         <v>15</v>
       </c>
     </row>
@@ -22276,7 +22421,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1894</v>
+        <v>1908</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22289,7 +22434,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1895</v>
+        <v>1909</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -22302,28 +22447,28 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1896</v>
+        <v>1910</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1897</v>
+        <v>1911</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1898</v>
+        <v>1912</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1899</v>
+        <v>1913</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1900</v>
+        <v>1914</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1901</v>
+        <v>1915</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>1902</v>
+        <v>1916</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1903</v>
+        <v>1917</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>8</v>
@@ -22331,7 +22476,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>1904</v>
+        <v>1918</v>
       </c>
       <c r="B5" s="21">
         <v>36.2</v>
@@ -22351,10 +22496,10 @@
         <v>48.8</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1905</v>
+        <v>1919</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>1906</v>
+        <v>1920</v>
       </c>
       <c r="I5" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-EAW-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-EAW-Prototype.html")</f>
@@ -22363,7 +22508,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>1907</v>
+        <v>1921</v>
       </c>
       <c r="B6" s="21">
         <v>41.7</v>
@@ -22383,10 +22528,10 @@
         <v>46.3</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>1908</v>
+        <v>1922</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1909</v>
+        <v>1923</v>
       </c>
       <c r="I6" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-TERA-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-TERA-Prototype.html")</f>
@@ -22395,7 +22540,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>1910</v>
+        <v>1924</v>
       </c>
       <c r="B7" s="21">
         <v>46.4</v>
@@ -22415,10 +22560,10 @@
         <v>41.6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>1905</v>
+        <v>1919</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1911</v>
+        <v>1925</v>
       </c>
       <c r="I7" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-EAWK-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-EAWK-Prototype.html")</f>
@@ -22427,7 +22572,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>1912</v>
+        <v>1926</v>
       </c>
       <c r="B8" s="21">
         <v>47.1</v>
@@ -22447,10 +22592,10 @@
         <v>37.9</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1905</v>
+        <v>1919</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1913</v>
+        <v>1927</v>
       </c>
       <c r="I8" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-MINUTA-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-MINUTA-Prototype.html")</f>
@@ -22459,7 +22604,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>1914</v>
+        <v>1928</v>
       </c>
       <c r="B9" s="24">
         <v>47.1</v>
@@ -22479,10 +22624,10 @@
         <v>42.9</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>1915</v>
+        <v>1929</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>1916</v>
+        <v>1930</v>
       </c>
       <c r="I9" s="27" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-MINUTA-V2-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-MINUTA-V2-Prototype.html")</f>
@@ -22491,7 +22636,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>1917</v>
+        <v>1931</v>
       </c>
       <c r="B10" s="21">
         <v>48.6</v>
@@ -22511,10 +22656,10 @@
         <v>39.4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1905</v>
+        <v>1919</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1918</v>
+        <v>1932</v>
       </c>
       <c r="I10" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-ORDER-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-ORDER-Prototype.html")</f>
@@ -22523,7 +22668,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>1919</v>
+        <v>1933</v>
       </c>
       <c r="B11" s="21">
         <v>54.5</v>
@@ -22543,10 +22688,10 @@
         <v>35.5</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1920</v>
+        <v>1934</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1921</v>
+        <v>1935</v>
       </c>
       <c r="I11" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-VERIF-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-VERIF-Prototype.html")</f>
@@ -22555,7 +22700,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>1922</v>
+        <v>1936</v>
       </c>
       <c r="B12" s="21">
         <v>54.8</v>
@@ -22575,10 +22720,10 @@
         <v>33.2</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>1908</v>
+        <v>1922</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1923</v>
+        <v>1937</v>
       </c>
       <c r="I12" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-CA-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-CA-Prototype.html")</f>
@@ -22587,7 +22732,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>1924</v>
+        <v>1938</v>
       </c>
       <c r="B13" s="21">
         <v>68.6</v>
@@ -22607,10 +22752,10 @@
         <v>23.400000000000006</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1920</v>
+        <v>1934</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1925</v>
+        <v>1939</v>
       </c>
       <c r="I13" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-ONBOARDING-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-ONBOARDING-Prototype.html")</f>
@@ -22639,10 +22784,10 @@
         <v>20.5</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>1905</v>
+        <v>1919</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1926</v>
+        <v>1940</v>
       </c>
       <c r="I14" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-ONBOARDING-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-ONBOARDING-Prototype.html")</f>
@@ -22651,7 +22796,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>1927</v>
+        <v>1941</v>
       </c>
       <c r="B15" s="21">
         <v>79.5</v>
@@ -22671,10 +22816,10 @@
         <v>15.5</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>1920</v>
+        <v>1934</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1925</v>
+        <v>1939</v>
       </c>
       <c r="I15" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-USER-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-USER-Prototype.html")</f>
@@ -22703,10 +22848,10 @@
         <v>5.299999999999997</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>1920</v>
+        <v>1934</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>1925</v>
+        <v>1939</v>
       </c>
       <c r="I16" s="8" t="str">
         <f>HYPERLINK("https://he-eppat.vercel.app/Backlog-HE-ONBOARDING-Prototype.html","https://he-eppat.vercel.app/Backlog-HE-ONBOARDING-Prototype.html")</f>
@@ -22715,7 +22860,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>1928</v>
+        <v>1942</v>
       </c>
       <c r="B17" s="29">
         <f>AVERAGE(B5,B6,B7,B10,B11,B12,B13,B14,B15,B16,B8)</f>
@@ -22741,7 +22886,7 @@
         <v>27</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>1929</v>
+        <v>1943</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>27</v>
@@ -22749,7 +22894,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>1930</v>
+        <v>1944</v>
       </c>
       <c r="B18" s="29">
         <f>AVERAGE(B5,B6,B7,B10,B11,B12,B13,B14,B15,B16,B9)</f>
@@ -22775,7 +22920,7 @@
         <v>27</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="I18" s="28" t="s">
         <v>27</v>
@@ -22786,25 +22931,25 @@
         <v>523</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1897</v>
+        <v>1911</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1898</v>
+        <v>1912</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1899</v>
+        <v>1913</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1900</v>
+        <v>1914</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1901</v>
+        <v>1915</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>27</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>27</v>
@@ -22812,7 +22957,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1933</v>
+        <v>1947</v>
       </c>
       <c r="B21" s="31">
         <v>85.9</v>
@@ -22835,7 +22980,7 @@
         <v>27</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>1934</v>
+        <v>1948</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>27</v>
@@ -22843,7 +22988,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1935</v>
+        <v>1949</v>
       </c>
       <c r="B22" s="31">
         <v>49.1</v>
@@ -22866,7 +23011,7 @@
         <v>27</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>1936</v>
+        <v>1950</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>27</v>
@@ -22874,7 +23019,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1937</v>
+        <v>1951</v>
       </c>
       <c r="B23" s="31">
         <v>65.9</v>
@@ -22897,7 +23042,7 @@
         <v>27</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>1938</v>
+        <v>1952</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>27</v>
@@ -22905,7 +23050,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1939</v>
+        <v>1953</v>
       </c>
       <c r="B24" s="31">
         <v>48.8</v>
@@ -22928,7 +23073,7 @@
         <v>27</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>1940</v>
+        <v>1954</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>27</v>
@@ -22936,7 +23081,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>1941</v>
+        <v>1955</v>
       </c>
       <c r="B25" s="31">
         <v>62.7</v>
@@ -22959,7 +23104,7 @@
         <v>27</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>1942</v>
+        <v>1956</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>27</v>
@@ -22967,7 +23112,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>1943</v>
+        <v>1957</v>
       </c>
       <c r="B26" s="31">
         <v>40.9</v>
@@ -22990,7 +23135,7 @@
         <v>27</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>1944</v>
+        <v>1958</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>27</v>
@@ -22998,7 +23143,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>1945</v>
+        <v>1959</v>
       </c>
       <c r="B27" s="31">
         <v>68.9</v>
@@ -23021,7 +23166,7 @@
         <v>27</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>1946</v>
+        <v>1960</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>27</v>
@@ -23029,7 +23174,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>1947</v>
+        <v>1961</v>
       </c>
       <c r="B28" s="31">
         <v>56.4</v>
@@ -23052,7 +23197,7 @@
         <v>27</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>1948</v>
+        <v>1962</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>27</v>
@@ -23060,7 +23205,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>1949</v>
+        <v>1963</v>
       </c>
       <c r="B29" s="31">
         <v>60.6</v>
@@ -23083,7 +23228,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>1950</v>
+        <v>1964</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>27</v>
@@ -23091,7 +23236,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>1951</v>
+        <v>1965</v>
       </c>
       <c r="B30" s="31">
         <v>10.6</v>
@@ -23114,7 +23259,7 @@
         <v>27</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>1952</v>
+        <v>1966</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>27</v>
@@ -23122,7 +23267,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>1953</v>
+        <v>1967</v>
       </c>
       <c r="B31" s="31">
         <v>90.9</v>
@@ -23145,7 +23290,7 @@
         <v>27</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>1954</v>
+        <v>1968</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>27</v>
@@ -23153,12 +23298,12 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>1955</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>1956</v>
+        <v>1970</v>
       </c>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -23171,7 +23316,7 @@
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
-        <v>1957</v>
+        <v>1971</v>
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -23184,7 +23329,7 @@
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -23197,7 +23342,7 @@
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
-        <v>1959</v>
+        <v>1973</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -23224,7 +23369,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -23235,7 +23380,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1960</v>
+        <v>1974</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -23243,7 +23388,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1961</v>
+        <v>1975</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23251,16 +23396,16 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>1962</v>
+        <v>1976</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>517</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1963</v>
+        <v>1977</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1964</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -23268,13 +23413,13 @@
         <v>46318</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1965</v>
+        <v>1979</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1966</v>
+        <v>1980</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1967</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -23282,13 +23427,13 @@
         <v>46318</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1965</v>
+        <v>1979</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1968</v>
+        <v>1982</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1967</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -23299,10 +23444,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1969</v>
+        <v>1983</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1970</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -23313,10 +23458,10 @@
         <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1971</v>
+        <v>1985</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1972</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -23327,10 +23472,10 @@
         <v>531</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1973</v>
+        <v>1987</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1974</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -23338,13 +23483,13 @@
         <v>46318</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1976</v>
+        <v>1990</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1972</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -23352,13 +23497,13 @@
         <v>46318</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1977</v>
+        <v>1991</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1978</v>
+        <v>1992</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1972</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -23369,10 +23514,10 @@
         <v>598</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1979</v>
+        <v>1993</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1972</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -23380,13 +23525,13 @@
         <v>46318</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1980</v>
+        <v>1994</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1981</v>
+        <v>1995</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1982</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -23394,13 +23539,13 @@
         <v>46318</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1983</v>
+        <v>1997</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1984</v>
+        <v>1998</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1982</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -23411,10 +23556,10 @@
         <v>22</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1985</v>
+        <v>1999</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1986</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -23425,10 +23570,10 @@
         <v>22</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1987</v>
+        <v>2001</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1988</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -23439,10 +23584,10 @@
         <v>91</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1989</v>
+        <v>2003</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1986</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -23453,10 +23598,10 @@
         <v>91</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1990</v>
+        <v>2004</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1986</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -23467,10 +23612,10 @@
         <v>22</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1991</v>
+        <v>2005</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1992</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -23478,13 +23623,13 @@
         <v>46318</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1993</v>
+        <v>2007</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1994</v>
+        <v>2008</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1995</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -23495,10 +23640,10 @@
         <v>22</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1996</v>
+        <v>2010</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1997</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -23506,13 +23651,13 @@
         <v>46318</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1999</v>
+        <v>2013</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2000</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -23520,13 +23665,13 @@
         <v>46318</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2003</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -23534,13 +23679,13 @@
         <v>46321</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2005</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -23548,13 +23693,13 @@
         <v>46321</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2007</v>
+        <v>2021</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>2008</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -23565,10 +23710,10 @@
         <v>22</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>2009</v>
+        <v>2023</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>2010</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -23576,13 +23721,13 @@
         <v>46321</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2012</v>
+        <v>2026</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>2013</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -23593,10 +23738,10 @@
         <v>777</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>2014</v>
+        <v>2028</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>2013</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -23607,10 +23752,10 @@
         <v>811</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>2015</v>
+        <v>2029</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>2016</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -23621,10 +23766,10 @@
         <v>819</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>2017</v>
+        <v>2031</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>2016</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -23635,10 +23780,10 @@
         <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>2018</v>
+        <v>2032</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>2019</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -23649,10 +23794,10 @@
         <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>2020</v>
+        <v>2034</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>2021</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -23660,13 +23805,13 @@
         <v>46321</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>2022</v>
+        <v>2036</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>2023</v>
+        <v>2037</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>2024</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -23674,13 +23819,13 @@
         <v>46321</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>2026</v>
+        <v>2040</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>2024</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -23691,10 +23836,10 @@
         <v>745</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>2027</v>
+        <v>2041</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>2028</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -23705,10 +23850,10 @@
         <v>836</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>2029</v>
+        <v>2043</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>2024</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -23716,13 +23861,13 @@
         <v>46321</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>2030</v>
+        <v>2044</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2031</v>
+        <v>2045</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>2032</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -23730,13 +23875,13 @@
         <v>46321</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>2033</v>
+        <v>2047</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>2034</v>
+        <v>2048</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>2035</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -23744,13 +23889,13 @@
         <v>46321</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>2036</v>
+        <v>2050</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2037</v>
+        <v>2051</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>2038</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -23758,13 +23903,13 @@
         <v>46321</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>2039</v>
+        <v>2053</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>2040</v>
+        <v>2054</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>1974</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -23772,13 +23917,13 @@
         <v>46321</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>2041</v>
+        <v>2055</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>2042</v>
+        <v>2056</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>2043</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -23786,13 +23931,13 @@
         <v>46321</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>2044</v>
+        <v>2058</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>2045</v>
+        <v>2059</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>2046</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -23803,10 +23948,10 @@
         <v>101</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>2047</v>
+        <v>2061</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>2048</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -23814,13 +23959,13 @@
         <v>46321</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>2049</v>
+        <v>2063</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>2050</v>
+        <v>2064</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>1982</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -23828,13 +23973,13 @@
         <v>46321</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>2051</v>
+        <v>2065</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>2052</v>
+        <v>2066</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>2053</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -23845,7 +23990,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>2054</v>
+        <v>2068</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>40</v>
@@ -23859,10 +24004,10 @@
         <v>1128</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>2055</v>
+        <v>2069</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>2053</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -23870,13 +24015,13 @@
         <v>46321</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>2056</v>
+        <v>2070</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>2057</v>
+        <v>2071</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>2058</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -23884,13 +24029,13 @@
         <v>46321</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>2059</v>
+        <v>2073</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>2060</v>
+        <v>2074</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>2061</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -23898,13 +24043,13 @@
         <v>46321</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>2064</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -23912,13 +24057,13 @@
         <v>46321</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>2065</v>
+        <v>2079</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>2066</v>
+        <v>2080</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>2067</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -23929,10 +24074,10 @@
         <v>61</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>2068</v>
+        <v>2082</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>2069</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -23940,13 +24085,13 @@
         <v>46321</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2070</v>
+        <v>2084</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>2071</v>
+        <v>2085</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>2072</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -23954,13 +24099,13 @@
         <v>46321</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>2073</v>
+        <v>2087</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>2074</v>
+        <v>2088</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>2075</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -23971,10 +24116,10 @@
         <v>1326</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>2076</v>
+        <v>2090</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>2077</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -23985,10 +24130,10 @@
         <v>1331</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>2079</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -23996,13 +24141,13 @@
         <v>46321</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>2080</v>
+        <v>2094</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>2081</v>
+        <v>2095</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>2082</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -24010,13 +24155,13 @@
         <v>46321</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>2083</v>
+        <v>2097</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>2084</v>
+        <v>2098</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>2085</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -24024,13 +24169,13 @@
         <v>46321</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>2086</v>
+        <v>2100</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>2087</v>
+        <v>2101</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>2088</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -24038,13 +24183,13 @@
         <v>46321</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>2090</v>
+        <v>2104</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>2091</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -24052,13 +24197,13 @@
         <v>46321</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>2092</v>
+        <v>2106</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>2093</v>
+        <v>2107</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>2094</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -24066,13 +24211,13 @@
         <v>46321</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>2095</v>
+        <v>2109</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>2096</v>
+        <v>2110</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>2097</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -24080,13 +24225,13 @@
         <v>46321</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>2098</v>
+        <v>2112</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>2099</v>
+        <v>2113</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>2100</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -24094,13 +24239,13 @@
         <v>46321</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>2101</v>
+        <v>2115</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>2102</v>
+        <v>2116</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>2100</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -24108,13 +24253,13 @@
         <v>46321</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>2103</v>
+        <v>2117</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>2104</v>
+        <v>2118</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>2105</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -24122,13 +24267,13 @@
         <v>46321</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>2106</v>
+        <v>2120</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>2107</v>
+        <v>2121</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>2108</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -24139,10 +24284,10 @@
         <v>1339</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>2109</v>
+        <v>2123</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>2110</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -24153,10 +24298,10 @@
         <v>1339</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>2111</v>
+        <v>2125</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>2112</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -24164,13 +24309,13 @@
         <v>46322</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>2113</v>
+        <v>2127</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>2114</v>
+        <v>2128</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>2115</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -24181,10 +24326,10 @@
         <v>712</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>2116</v>
+        <v>2130</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>2117</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -24195,10 +24340,10 @@
         <v>712</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>2118</v>
+        <v>2132</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>2119</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -24209,10 +24354,10 @@
         <v>1339</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>2120</v>
+        <v>2134</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>2121</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -24223,10 +24368,24 @@
         <v>22</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>2122</v>
+        <v>2136</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>2123</v>
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="35">
+        <v>46322</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>2140</v>
       </c>
     </row>
   </sheetData>
@@ -24250,19 +24409,19 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2124</v>
+        <v>2141</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2125</v>
+        <v>2142</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>2126</v>
+        <v>2143</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>27</v>
@@ -24270,66 +24429,66 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>2127</v>
+        <v>2144</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>2128</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
-        <v>1881</v>
+        <v>1895</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>2129</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>2130</v>
+        <v>2147</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>2131</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>2132</v>
+        <v>2149</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>2133</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>2134</v>
+        <v>2151</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>2135</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>2136</v>
+        <v>2153</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>2137</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>2138</v>
+        <v>2155</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>2139</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>2140</v>
+        <v>2157</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>2141</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -24342,7 +24501,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>2142</v>
+        <v>2159</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>27</v>
@@ -24350,26 +24509,26 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>2143</v>
+        <v>2160</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>2144</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>2145</v>
+        <v>2162</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>2146</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>2147</v>
+        <v>2164</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>2148</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -24377,7 +24536,7 @@
         <v>517</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>2149</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -24385,7 +24544,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>2150</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -24406,10 +24565,10 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>1886</v>
+        <v>1900</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>2151</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -24417,7 +24576,7 @@
         <v>541</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>2152</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -24425,39 +24584,39 @@
         <v>550</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>2153</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="37" t="s">
-        <v>1887</v>
+        <v>1901</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>2154</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>1888</v>
+        <v>1902</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>2155</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="37" t="s">
-        <v>1889</v>
+        <v>1903</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>2156</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>1890</v>
+        <v>1904</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>2157</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -24470,7 +24629,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
-        <v>2158</v>
+        <v>2175</v>
       </c>
       <c r="B30" s="36" t="s">
         <v>27</v>
@@ -24478,90 +24637,90 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="37" t="s">
-        <v>2159</v>
+        <v>2176</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>1933</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
-        <v>2160</v>
+        <v>2177</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>1935</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
-        <v>2161</v>
+        <v>2178</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>1937</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>2162</v>
+        <v>2179</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1939</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
-        <v>2163</v>
+        <v>2180</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>2164</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>2165</v>
+        <v>2182</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1943</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
-        <v>2166</v>
+        <v>2183</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1945</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>2167</v>
+        <v>2184</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1947</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
-        <v>2168</v>
+        <v>2185</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1949</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>2169</v>
+        <v>2186</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1951</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
-        <v>2170</v>
+        <v>2187</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1953</v>
+        <v>1967</v>
       </c>
     </row>
   </sheetData>

--- a/Backlog-HE-EPPAT-Peruri.xlsx
+++ b/Backlog-HE-EPPAT-Peruri.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3625" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3631" uniqueCount="2192">
   <si>
     <t>Panduan Penerapan IDDS untuk Developer E-PPAT</t>
   </si>
@@ -6798,6 +6798,18 @@
   </si>
   <si>
     <t>sumber/tema-proto.html; sumber/rakit-idds.js; prototipe/Backlog-IDDS-TN-CMS-Prototype.html; Backlog-IDDS-PL-SISTEM-Prototype.html; semua prototipe</t>
+  </si>
+  <si>
+    <t>Tema INAgov dan Default memakai latar polos netral IDDS (--ina-background-secondary) di semua halaman, termasuk halaman Masuk tenant dan platform. Latar bergambar khas E-PPAT (gradasi dengan watermark IPPAT) hanya dipakai tema E-PPAT. Token warna INAgov dan Default sudah dicocokkan dengan CSS resmi IDDS 1.6.38 (0 perbedaan).</t>
+  </si>
+  <si>
+    <t>sumber/tema-proto.html; semua prototipe</t>
+  </si>
+  <si>
+    <t>Saat pengguna membuka editor Penyusunan Akta v2, menu samping otomatis diciutkan menjadi ikon (72 px) agar kertas lebih lega. Saat kembali ke daftar, menu samping mengikuti pilihan terakhir pengguna. Ciut otomatis ini tidak menimpa pilihan tersimpan dan tidak berlaku di ponsel karena menu samping sudah berupa laci. Ikon catatan pada Navigasi diganti dengan ikon Tabler pilcrow.</t>
+  </si>
+  <si>
+    <t>sumber/sidebar-idds.html; sumber/minuta2-badan.html; prototipe/Backlog-HE-MINUTA-V2-Prototype.html; semua prototipe bersidebar</t>
   </si>
   <si>
     <t>Keterangan</t>
@@ -23369,7 +23381,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -24386,6 +24398,34 @@
       </c>
       <c r="D74" s="6" t="s">
         <v>2140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="35">
+        <v>46322</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="35">
+        <v>46323</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>2144</v>
       </c>
     </row>
   </sheetData>
@@ -24409,19 +24449,19 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2141</v>
+        <v>2145</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>2143</v>
+        <v>2147</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>27</v>
@@ -24429,10 +24469,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>2144</v>
+        <v>2148</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>2145</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -24440,55 +24480,55 @@
         <v>1895</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -24501,7 +24541,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>2159</v>
+        <v>2163</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>27</v>
@@ -24509,26 +24549,26 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>2160</v>
+        <v>2164</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>2161</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>2163</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>2165</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -24536,7 +24576,7 @@
         <v>517</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>2166</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -24544,7 +24584,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>2167</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -24568,7 +24608,7 @@
         <v>1900</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>2168</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -24576,7 +24616,7 @@
         <v>541</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>2169</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -24584,7 +24624,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>2170</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -24592,7 +24632,7 @@
         <v>1901</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -24600,7 +24640,7 @@
         <v>1902</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -24608,7 +24648,7 @@
         <v>1903</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -24616,7 +24656,7 @@
         <v>1904</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>2174</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -24629,7 +24669,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
-        <v>2175</v>
+        <v>2179</v>
       </c>
       <c r="B30" s="36" t="s">
         <v>27</v>
@@ -24637,7 +24677,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="37" t="s">
-        <v>2176</v>
+        <v>2180</v>
       </c>
       <c r="B31" s="37" t="s">
         <v>1947</v>
@@ -24645,7 +24685,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
-        <v>2177</v>
+        <v>2181</v>
       </c>
       <c r="B32" s="37" t="s">
         <v>1949</v>
@@ -24653,7 +24693,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
-        <v>2178</v>
+        <v>2182</v>
       </c>
       <c r="B33" s="37" t="s">
         <v>1951</v>
@@ -24661,7 +24701,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="B34" s="37" t="s">
         <v>1953</v>
@@ -24669,15 +24709,15 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>2181</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>2182</v>
+        <v>2186</v>
       </c>
       <c r="B36" s="37" t="s">
         <v>1957</v>
@@ -24685,7 +24725,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
-        <v>2183</v>
+        <v>2187</v>
       </c>
       <c r="B37" s="37" t="s">
         <v>1959</v>
@@ -24693,7 +24733,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>2184</v>
+        <v>2188</v>
       </c>
       <c r="B38" s="37" t="s">
         <v>1961</v>
@@ -24701,7 +24741,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
-        <v>2185</v>
+        <v>2189</v>
       </c>
       <c r="B39" s="37" t="s">
         <v>1963</v>
@@ -24709,7 +24749,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="B40" s="37" t="s">
         <v>1965</v>
@@ -24717,7 +24757,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
-        <v>2187</v>
+        <v>2191</v>
       </c>
       <c r="B41" s="37" t="s">
         <v>1967</v>

--- a/Backlog-HE-EPPAT-Peruri.xlsx
+++ b/Backlog-HE-EPPAT-Peruri.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3631" uniqueCount="2192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3634" uniqueCount="2195">
   <si>
     <t>Panduan Penerapan IDDS untuk Developer E-PPAT</t>
   </si>
@@ -6810,6 +6810,15 @@
   </si>
   <si>
     <t>sumber/sidebar-idds.html; sumber/minuta2-badan.html; prototipe/Backlog-HE-MINUTA-V2-Prototype.html; semua prototipe bersidebar</t>
+  </si>
+  <si>
+    <t>IDDS-TN-40; IDDS-PL-41</t>
+  </si>
+  <si>
+    <t>Tombol menu (ikon tiga garis) di header kini hanya tampil di layar sempit untuk membuka laci menu samping. Di layar lebar tombol itu disembunyikan karena tidak berfungsi; menu samping diciutkan atau dibentangkan dengan tombol di kepala menu samping. Dengan begitu, setiap ukuran layar hanya punya satu kendali menu samping.</t>
+  </si>
+  <si>
+    <t>sumber/sidebar-idds.html; semua prototipe bersidebar</t>
   </si>
   <si>
     <t>Keterangan</t>
@@ -23381,7 +23390,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -24426,6 +24435,20 @@
       </c>
       <c r="D76" s="6" t="s">
         <v>2144</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="35">
+        <v>46323</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>2147</v>
       </c>
     </row>
   </sheetData>
@@ -24449,19 +24472,19 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>27</v>
@@ -24469,10 +24492,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -24480,55 +24503,55 @@
         <v>1895</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -24541,7 +24564,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>27</v>
@@ -24549,26 +24572,26 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -24576,7 +24599,7 @@
         <v>517</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -24584,7 +24607,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -24608,7 +24631,7 @@
         <v>1900</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -24616,7 +24639,7 @@
         <v>541</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -24624,7 +24647,7 @@
         <v>550</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -24632,7 +24655,7 @@
         <v>1901</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -24640,7 +24663,7 @@
         <v>1902</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -24648,7 +24671,7 @@
         <v>1903</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -24656,7 +24679,7 @@
         <v>1904</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -24669,7 +24692,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="B30" s="36" t="s">
         <v>27</v>
@@ -24677,7 +24700,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="37" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="B31" s="37" t="s">
         <v>1947</v>
@@ -24685,7 +24708,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="B32" s="37" t="s">
         <v>1949</v>
@@ -24693,7 +24716,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="B33" s="37" t="s">
         <v>1951</v>
@@ -24701,7 +24724,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="B34" s="37" t="s">
         <v>1953</v>
@@ -24709,15 +24732,15 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="B36" s="37" t="s">
         <v>1957</v>
@@ -24725,7 +24748,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="B37" s="37" t="s">
         <v>1959</v>
@@ -24733,7 +24756,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="B38" s="37" t="s">
         <v>1961</v>
@@ -24741,7 +24764,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="B39" s="37" t="s">
         <v>1963</v>
@@ -24749,7 +24772,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="B40" s="37" t="s">
         <v>1965</v>
@@ -24757,7 +24780,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="37" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="B41" s="37" t="s">
         <v>1967</v>
